--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\OneDrive\Documents\Projects\Verilog\Fat Cat CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1479696-692C-4C22-AA5C-A037AEC19872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF44D417-F050-4B96-B35E-2403A0A2796A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="139">
   <si>
     <t>Opcode</t>
   </si>
@@ -292,9 +292,6 @@
     <t>c=0,Sets flags</t>
   </si>
   <si>
-    <t>Flags only get updated after CMP (1111)</t>
-  </si>
-  <si>
     <t>00010 addr8 rd</t>
   </si>
   <si>
@@ -344,6 +341,108 @@
   </si>
   <si>
     <t>No Operation (Temporary, may change)</t>
+  </si>
+  <si>
+    <t>10000 00000000000</t>
+  </si>
+  <si>
+    <t>Addition: rs + rt → rd</t>
+  </si>
+  <si>
+    <t>Subtraction: rs − rt → rd</t>
+  </si>
+  <si>
+    <t>Multiplication: rs * rt → rd</t>
+  </si>
+  <si>
+    <t>Negation: -rs -&gt; rd or ~rs + 1 -&gt; rd</t>
+  </si>
+  <si>
+    <t>Add Immediate: rs + imm5 → rd</t>
+  </si>
+  <si>
+    <t>Mutliply Immediate: rs * imm5 → rd</t>
+  </si>
+  <si>
+    <t>Bitwise AND: rs &amp; rt → rd</t>
+  </si>
+  <si>
+    <t>Bitwise OR: rs | rt → rd</t>
+  </si>
+  <si>
+    <t>Bitwise NOT: ~rs → rd</t>
+  </si>
+  <si>
+    <t>Bitwise XOR: rs ^ rt → rd</t>
+  </si>
+  <si>
+    <t>Logical shift left: rs &lt;&lt; rt → rd</t>
+  </si>
+  <si>
+    <t>Logical shift right: rs &gt;&gt; rt → rd</t>
+  </si>
+  <si>
+    <t>Arithmetic shift right: rs &gt;&gt;&gt; rt → rd</t>
+  </si>
+  <si>
+    <t>Pass through: c=a</t>
+  </si>
+  <si>
+    <t>Compare: rs-rt Sets Flags Z,C,S,O</t>
+  </si>
+  <si>
+    <t>10001 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>10010 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>10011 rs 000 00 rd</t>
+  </si>
+  <si>
+    <t>10100 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>10101 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>10110 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>10111 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>11000 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>11001 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>11010 rs rt 00 rd</t>
+  </si>
+  <si>
+    <t>11011 rs 000 00 rd</t>
+  </si>
+  <si>
+    <t>11100 rs imm5 rd</t>
+  </si>
+  <si>
+    <t>11101 rs imm5 rd</t>
+  </si>
+  <si>
+    <t>11111 rs rt 00000</t>
+  </si>
+  <si>
+    <t>SUBI</t>
+  </si>
+  <si>
+    <t>Subtract Immediate: rs - imm5 → rd</t>
+  </si>
+  <si>
+    <t>11110 rs imm5 rd</t>
+  </si>
+  <si>
+    <t>Updates Flags</t>
   </si>
 </sst>
 </file>
@@ -389,12 +488,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,6 +517,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -676,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -746,10 +869,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" t="s">
         <v>90</v>
-      </c>
-      <c r="F3" t="s">
-        <v>91</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -769,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -792,7 +915,7 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -815,7 +938,7 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
         <v>40</v>
@@ -838,7 +961,7 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
@@ -861,7 +984,7 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -881,7 +1004,7 @@
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -901,7 +1024,7 @@
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -915,7 +1038,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -929,7 +1052,7 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -943,7 +1066,7 @@
         <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -957,7 +1080,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -968,10 +1091,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -982,10 +1105,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -996,56 +1119,235 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D19" s="3"/>
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D20" s="3"/>
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D21" s="3"/>
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D22" s="3"/>
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D23" s="3"/>
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D24" s="3"/>
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D25" s="3"/>
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D26" s="3"/>
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D27" s="3"/>
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="3"/>
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D29" s="3"/>
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D30" s="3"/>
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="3"/>
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="3"/>
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1056,12 +1358,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465292AB-E6A7-4E56-A7C6-DDCDEB24DFE9}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="11.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="8" max="8" width="10.77734375" customWidth="1"/>
   </cols>
@@ -1076,6 +1379,9 @@
       <c r="C1" t="s">
         <v>51</v>
       </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
       <c r="H1" t="s">
         <v>82</v>
       </c>
@@ -1090,6 +1396,9 @@
       <c r="C2" t="s">
         <v>70</v>
       </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="F2" t="s">
         <v>67</v>
       </c>
@@ -1107,6 +1416,9 @@
       <c r="C3" t="s">
         <v>71</v>
       </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="F3" t="s">
         <v>68</v>
       </c>
@@ -1124,6 +1436,9 @@
       <c r="C4" t="s">
         <v>72</v>
       </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="F4" t="s">
         <v>69</v>
       </c>
@@ -1141,6 +1456,9 @@
       <c r="C5" t="s">
         <v>73</v>
       </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="H5" t="s">
         <v>85</v>
       </c>
@@ -1155,8 +1473,8 @@
       <c r="C6" t="s">
         <v>74</v>
       </c>
-      <c r="F6" t="s">
-        <v>88</v>
+      <c r="D6" s="4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1169,6 +1487,9 @@
       <c r="C7" t="s">
         <v>75</v>
       </c>
+      <c r="D7" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -1180,6 +1501,9 @@
       <c r="C8" t="s">
         <v>76</v>
       </c>
+      <c r="D8" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
@@ -1191,6 +1515,9 @@
       <c r="C9" t="s">
         <v>77</v>
       </c>
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -1202,6 +1529,9 @@
       <c r="C10" t="s">
         <v>78</v>
       </c>
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
@@ -1213,6 +1543,9 @@
       <c r="C11" t="s">
         <v>79</v>
       </c>
+      <c r="D11" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
@@ -1224,6 +1557,9 @@
       <c r="C12" t="s">
         <v>80</v>
       </c>
+      <c r="D12" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
@@ -1235,6 +1571,9 @@
       <c r="C13" t="s">
         <v>81</v>
       </c>
+      <c r="D13" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
@@ -1246,6 +1585,9 @@
       <c r="C14" t="s">
         <v>78</v>
       </c>
+      <c r="D14" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
@@ -1255,18 +1597,38 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="D15" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
+        <v>1110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>1111</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>87</v>
+      </c>
+      <c r="D17" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\OneDrive\Documents\Projects\Verilog\Fat Cat CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF44D417-F050-4B96-B35E-2403A0A2796A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F60BB7D-72B4-484B-8998-877CAAAA0AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="162">
   <si>
     <t>Opcode</t>
   </si>
@@ -151,15 +151,9 @@
     <t>Each Instruction is 2 bytes (16 bits)</t>
   </si>
   <si>
-    <t>Max code length is 2048 Instructions (4096 bytes)</t>
-  </si>
-  <si>
     <t>Register addrs are 3 bit in length</t>
   </si>
   <si>
-    <t>Memory Addrs. Are 11 bits</t>
-  </si>
-  <si>
     <t>Branch if ZERO != 1 to addr*2</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>Jump and link (R7 = PC + 1;PC = addr*2) (function call)</t>
   </si>
   <si>
-    <t>00000 000 000 00 000</t>
-  </si>
-  <si>
     <t>Operation</t>
   </si>
   <si>
@@ -325,27 +316,9 @@
     <t>01011 addr11</t>
   </si>
   <si>
-    <t>01100 00000000000</t>
-  </si>
-  <si>
     <t>00011 addr8 rd</t>
   </si>
   <si>
-    <t>01101 00000000000</t>
-  </si>
-  <si>
-    <t>01110 00000000000</t>
-  </si>
-  <si>
-    <t>01111 00000000000</t>
-  </si>
-  <si>
-    <t>No Operation (Temporary, may change)</t>
-  </si>
-  <si>
-    <t>10000 00000000000</t>
-  </si>
-  <si>
     <t>Addition: rs + rt → rd</t>
   </si>
   <si>
@@ -391,58 +364,154 @@
     <t>Compare: rs-rt Sets Flags Z,C,S,O</t>
   </si>
   <si>
-    <t>10001 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>10010 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>10011 rs 000 00 rd</t>
-  </si>
-  <si>
-    <t>10100 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>10101 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>10110 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>10111 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>11000 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>11001 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>11010 rs rt 00 rd</t>
-  </si>
-  <si>
-    <t>11011 rs 000 00 rd</t>
-  </si>
-  <si>
     <t>11100 rs imm5 rd</t>
   </si>
   <si>
     <t>11101 rs imm5 rd</t>
   </si>
   <si>
-    <t>11111 rs rt 00000</t>
-  </si>
-  <si>
-    <t>SUBI</t>
-  </si>
-  <si>
-    <t>Subtract Immediate: rs - imm5 → rd</t>
-  </si>
-  <si>
     <t>11110 rs imm5 rd</t>
   </si>
   <si>
     <t>Updates Flags</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>Add with carry</t>
+  </si>
+  <si>
+    <t>c=a+b+carry</t>
+  </si>
+  <si>
+    <t>AND rs,rt,rd</t>
+  </si>
+  <si>
+    <t>OR  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>XOR  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>LSL  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>LSR  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>ASR  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>ADD  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>SUB  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>MUL  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>ADDI  rs,imm5,rd</t>
+  </si>
+  <si>
+    <t>ADC  rs,rt,rd</t>
+  </si>
+  <si>
+    <t>MULI  rs,imm5,rd</t>
+  </si>
+  <si>
+    <t>NEG  rs,rd</t>
+  </si>
+  <si>
+    <t>NOT rs,rd</t>
+  </si>
+  <si>
+    <t>00000 XXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>X means "don't care" bit, can be either 0 or 1</t>
+  </si>
+  <si>
+    <t>01100 XXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>10000 XXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>10001 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>10010 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>10011 rs XXX XX rd</t>
+  </si>
+  <si>
+    <t>10100 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>10101 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>10110 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>10111 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>11000 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>11001 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>11010 rs rt XX rd</t>
+  </si>
+  <si>
+    <t>11011 rs XXX XX rd</t>
+  </si>
+  <si>
+    <t>CMP rs,rt</t>
+  </si>
+  <si>
+    <t>11111 rs rt XXXXX</t>
+  </si>
+  <si>
+    <t>MOVE rs,rd</t>
+  </si>
+  <si>
+    <t>Sets register rd = rs</t>
+  </si>
+  <si>
+    <t>01101 rs XXX XX rd</t>
+  </si>
+  <si>
+    <t>LOADR rs, rd</t>
+  </si>
+  <si>
+    <t>Loads memory[rs] -&gt; rd</t>
+  </si>
+  <si>
+    <t>01110 rs XXX XX rd</t>
+  </si>
+  <si>
+    <t>STORER rs, rd</t>
+  </si>
+  <si>
+    <t>Stores rd -&gt; memory[rs]</t>
+  </si>
+  <si>
+    <t>01111 rs XXX XX rd</t>
+  </si>
+  <si>
+    <t>Max code length is 2048 Instructions</t>
+  </si>
+  <si>
+    <t>Instruction Memory Addrs. Are 11 bits, each word is 16 bits</t>
+  </si>
+  <si>
+    <t>Data Memory Addrs are 8 bits, each word is 8 bits</t>
   </si>
 </sst>
 </file>
@@ -806,7 +875,7 @@
     <col min="2" max="2" width="17.109375" customWidth="1"/>
     <col min="3" max="3" width="44.6640625" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="6" max="6" width="45.44140625" customWidth="1"/>
+    <col min="6" max="6" width="49.44140625" customWidth="1"/>
     <col min="7" max="7" width="4.5546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" customWidth="1"/>
     <col min="9" max="9" width="5.109375" customWidth="1"/>
@@ -846,10 +915,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -869,10 +938,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -892,10 +961,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -915,10 +984,10 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -938,10 +1007,10 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -958,13 +1027,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -981,10 +1050,13 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>159</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -1001,10 +1073,13 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
+        <v>134</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -1021,10 +1096,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1035,10 +1110,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1052,7 +1127,7 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1063,10 +1138,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1080,7 +1155,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1088,13 +1163,13 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1102,13 +1177,13 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1116,13 +1191,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1133,10 +1208,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1144,13 +1219,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1158,13 +1233,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1172,13 +1247,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1186,13 +1261,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1200,13 +1275,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1214,13 +1289,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1228,13 +1303,13 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1242,13 +1317,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1256,13 +1331,13 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1270,13 +1345,13 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1284,13 +1359,13 @@
         <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1298,13 +1373,13 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1312,13 +1387,13 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1326,13 +1401,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1340,13 +1415,13 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1377,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1391,19 +1466,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1411,19 +1486,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1431,19 +1506,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1451,16 +1526,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1468,10 +1543,10 @@
         <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>
@@ -1482,10 +1557,10 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -1496,10 +1571,10 @@
         <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -1510,10 +1585,10 @@
         <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -1524,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -1538,10 +1613,10 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -1552,10 +1627,10 @@
         <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
@@ -1566,10 +1641,10 @@
         <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="b">
         <v>1</v>
@@ -1580,10 +1655,10 @@
         <v>1100</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" s="4" t="b">
         <v>1</v>
@@ -1594,10 +1669,10 @@
         <v>1101</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D15" s="4" t="b">
         <v>1</v>
@@ -1608,10 +1683,10 @@
         <v>1110</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="D16" s="4" t="b">
         <v>1</v>
@@ -1622,10 +1697,10 @@
         <v>1111</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D17" s="4" t="b">
         <v>1</v>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\OneDrive\Documents\Projects\Verilog\Fat Cat CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F60BB7D-72B4-484B-8998-877CAAAA0AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F7849C-29B0-4F4A-B8BD-645AF145B3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="161">
   <si>
     <t>Opcode</t>
   </si>
@@ -211,12 +211,6 @@
     <t>CMP</t>
   </si>
   <si>
-    <t>ADDI</t>
-  </si>
-  <si>
-    <t>MULI</t>
-  </si>
-  <si>
     <t>NEG</t>
   </si>
   <si>
@@ -512,6 +506,9 @@
   </si>
   <si>
     <t>Data Memory Addrs are 8 bits, each word is 8 bits</t>
+  </si>
+  <si>
+    <t>c=0</t>
   </si>
 </sst>
 </file>
@@ -915,7 +912,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -938,10 +935,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -961,10 +958,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -984,10 +981,10 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1007,7 +1004,7 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -1030,7 +1027,7 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
@@ -1053,10 +1050,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -1076,10 +1073,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -1099,7 +1096,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1113,7 +1110,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1127,7 +1124,7 @@
         <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1141,7 +1138,7 @@
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1155,7 +1152,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1163,13 +1160,13 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" t="s">
         <v>150</v>
-      </c>
-      <c r="C15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1177,13 +1174,13 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" t="s">
         <v>153</v>
-      </c>
-      <c r="C16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1191,13 +1188,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" t="s">
         <v>156</v>
-      </c>
-      <c r="C17" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1208,10 +1205,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1219,13 +1216,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1233,13 +1230,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1247,13 +1244,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1261,13 +1258,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1275,13 +1272,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1289,13 +1286,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1303,13 +1300,13 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1317,13 +1314,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1331,13 +1328,13 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1345,13 +1342,13 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1359,13 +1356,13 @@
         <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1373,13 +1370,13 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1387,13 +1384,13 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1401,13 +1398,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1415,13 +1412,13 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1455,10 +1452,10 @@
         <v>48</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1469,16 +1466,16 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1489,16 +1486,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1509,16 +1506,16 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1529,13 +1526,13 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1546,7 +1543,7 @@
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>
@@ -1560,7 +1557,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -1574,7 +1571,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -1588,7 +1585,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -1602,7 +1599,7 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -1616,7 +1613,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -1630,7 +1627,7 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
@@ -1641,13 +1638,13 @@
         <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1655,13 +1652,13 @@
         <v>1100</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="D14" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1669,13 +1666,13 @@
         <v>1101</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="D15" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1683,10 +1680,10 @@
         <v>1110</v>
       </c>
       <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
         <v>116</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
       </c>
       <c r="D16" s="4" t="b">
         <v>1</v>
@@ -1700,7 +1697,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D17" s="4" t="b">
         <v>1</v>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\OneDrive\Documents\Projects\Verilog\Fat Cat CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F7849C-29B0-4F4A-B8BD-645AF145B3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698623D6-B239-40DA-B6B3-299D06E77DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="164">
   <si>
     <t>Opcode</t>
   </si>
@@ -508,7 +508,16 @@
     <t>Data Memory Addrs are 8 bits, each word is 8 bits</t>
   </si>
   <si>
-    <t>c=0</t>
+    <t>ADDI</t>
+  </si>
+  <si>
+    <t>MULI</t>
+  </si>
+  <si>
+    <t>Same as ADD</t>
+  </si>
+  <si>
+    <t>Same as MUL</t>
   </si>
 </sst>
 </file>
@@ -1652,13 +1661,13 @@
         <v>1100</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1666,13 +1675,13 @@
         <v>1101</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shubh\OneDrive\Documents\Projects\Verilog\Fat Cat CPU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698623D6-B239-40DA-B6B3-299D06E77DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5295E8-68F7-4313-B5EB-ADC226E1D87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="165">
   <si>
     <t>Opcode</t>
   </si>
@@ -43,9 +43,6 @@
     <t>NOP</t>
   </si>
   <si>
-    <t>No Operation</t>
-  </si>
-  <si>
     <t>Load memory[addr] → rd</t>
   </si>
   <si>
@@ -518,6 +515,12 @@
   </si>
   <si>
     <t>Same as MUL</t>
+  </si>
+  <si>
+    <t>HALT</t>
+  </si>
+  <si>
+    <t>Stops operation (default value in memory)</t>
   </si>
 </sst>
 </file>
@@ -889,7 +892,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -901,33 +904,33 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -935,22 +938,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
         <v>84</v>
       </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" s="1">
         <v>1</v>
@@ -958,22 +961,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1">
         <v>10</v>
@@ -981,22 +984,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I5" s="1">
         <v>11</v>
@@ -1004,22 +1007,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="1">
         <v>100</v>
@@ -1027,22 +1030,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" s="1">
         <v>101</v>
@@ -1050,22 +1053,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1">
         <v>110</v>
@@ -1073,22 +1076,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I9" s="1">
         <v>111</v>
@@ -1096,338 +1099,338 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" t="s">
         <v>148</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>149</v>
-      </c>
-      <c r="D15" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
         <v>151</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>152</v>
-      </c>
-      <c r="D16" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" t="s">
         <v>154</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1458,13 +1461,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1472,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1492,19 +1495,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1512,19 +1515,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1532,16 +1535,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1549,10 +1552,10 @@
         <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>
@@ -1563,10 +1566,10 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -1577,10 +1580,10 @@
         <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -1591,10 +1594,10 @@
         <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -1605,10 +1608,10 @@
         <v>1000</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -1619,10 +1622,10 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -1633,10 +1636,10 @@
         <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
@@ -1647,10 +1650,10 @@
         <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="4" t="b">
         <v>0</v>
@@ -1661,10 +1664,10 @@
         <v>1100</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="4" t="b">
         <v>1</v>
@@ -1675,10 +1678,10 @@
         <v>1101</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D15" s="4" t="b">
         <v>1</v>
@@ -1689,10 +1692,10 @@
         <v>1110</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="4" t="b">
         <v>1</v>
@@ -1703,10 +1706,10 @@
         <v>1111</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="4" t="b">
         <v>1</v>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -368,10 +368,10 @@
     <t>STORER rs, rd</t>
   </si>
   <si>
-    <t>Stores rt -&gt; memory[rs]</t>
-  </si>
-  <si>
-    <t>01111 rs rt XX XXX</t>
+    <t>Stores rd -&gt; memory[rs]</t>
+  </si>
+  <si>
+    <t>01111 rs XXX XX rd</t>
   </si>
   <si>
     <t>NOP</t>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -209,7 +209,7 @@
     <t>STORE addr, rd</t>
   </si>
   <si>
-    <t>Store rd → memory[addr]</t>
+    <t>Store rd → memory[addr] (rd gets converted rt internally)</t>
   </si>
   <si>
     <t>00010 addr8 rd</t>
@@ -368,7 +368,7 @@
     <t>STORER rs, rd</t>
   </si>
   <si>
-    <t>Stores rd -&gt; memory[rs]</t>
+    <t>Stores rd -&gt; memory[rs] (rd gets converted to rt internally)</t>
   </si>
   <si>
     <t>01111 rs XXX XX rd</t>

--- a/Instruction Set.xlsx
+++ b/Instruction Set.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makad\Documents\Projects\Verilog\Fat-Cat-CPU\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7770F511-51DD-40C9-9AD2-649B8E25ACCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="57480" yWindow="3510" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Instructions"/>
-    <sheet r:id="rId2" sheetId="2" name="ALU Opcode"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="ALU Opcode" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="166">
   <si>
     <t>Opcode</t>
   </si>
@@ -26,9 +32,6 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>Updates Flags</t>
-  </si>
-  <si>
     <t>Flags</t>
   </si>
   <si>
@@ -38,9 +41,6 @@
     <t>c=a</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>a is input 1</t>
   </si>
   <si>
@@ -92,9 +92,6 @@
     <t>c=a&lt;&lt;b</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>LSR</t>
   </si>
   <si>
@@ -516,12 +513,18 @@
   </si>
   <si>
     <t>11111 rs rt XXXXX</t>
+  </si>
+  <si>
+    <t>All opcodes update zero flag</t>
+  </si>
+  <si>
+    <t>Only CMP updates CSO flags</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0000"/>
     <numFmt numFmtId="165" formatCode="000"/>
@@ -568,53 +571,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -625,10 +617,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -666,71 +658,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -758,7 +750,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -781,11 +773,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -794,13 +786,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -810,7 +802,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -819,7 +811,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -828,7 +820,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -836,10 +828,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -904,704 +896,566 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="5.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="44.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="49.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="4.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="25.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="5.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="6">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="B4" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="C4" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="H4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="I4" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="B5" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="C5" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="I5" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="B6" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
+      <c r="C6" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="H6" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="I6" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="C7" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="8">
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="8">
+    <row r="13" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="8">
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="C16" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C24" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    </row>
+    <row r="29" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" t="s">
         <v>150</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C30" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
         <v>161</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1609,344 +1463,239 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="10.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3">
-        <v>100</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3">
-        <v>101</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="F7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3">
-        <v>110</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3">
-        <v>111</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3">
-        <v>1010</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3">
-        <v>1011</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>1101</v>
+      </c>
+      <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>1110</v>
+      </c>
+      <c r="B16" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3">
-        <v>1101</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>1111</v>
+      </c>
+      <c r="B17" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3">
-        <v>1110</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3">
-        <v>1111</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
